--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.150.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.150.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.150.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.150.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="60" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -606,11 +606,15 @@
       <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L58: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ heirs or</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]143</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]143</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L28: isolated marker/symbol line :: 6</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: :</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]143</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -628,7 +632,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • heirs or</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr">
         <is>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>85</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -665,7 +673,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L58: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • heirs or</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -677,7 +685,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: .(</t>
+          <t>L51: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -720,7 +728,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L95: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -728,7 +736,7 @@
       <c r="N4" s="1" t="inlineStr"/>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L80: isolated marker/symbol line :: .(</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -755,7 +763,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -765,13 +773,17 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr"/>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: *</t>
+          <t>L95: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -814,7 +826,7 @@
       <c r="N6" s="1" t="inlineStr"/>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: a</t>
+          <t>L97: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -857,7 +869,7 @@
       <c r="N7" s="1" t="inlineStr"/>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L99: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -898,7 +910,11 @@
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr"/>
-      <c r="O8" s="1" t="inlineStr"/>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
@@ -962,7 +978,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1001,7 +1017,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1040,7 +1056,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1118,7 +1134,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
